--- a/光伏配储项目/电价数据/2026/观桥站.xlsx
+++ b/光伏配储项目/电价数据/2026/观桥站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.50989</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38354</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7218300000000001</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.56477</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5172599999999999</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.45409</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.44875</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43786</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45467</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43943</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42325</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41947</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40892</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39846</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38526</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40216</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.4234</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41288</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39182</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38511</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41728</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39204</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42075</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41424</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42423</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41306</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44425</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.35765</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.29991</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.26808</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29488</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30016</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.21531</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.25906</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.07740999999999999</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.06353</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.05198</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.03262</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.05381</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.03901</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.04514</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.00925</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.01627</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08624</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.00087</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.00357</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14525</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.213</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.23617</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.21431</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.11631</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.00371</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.006849999999999999</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.15691</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>-0.01781</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.19181</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.22368</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>-0.02607</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.00835</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.12331</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.19501</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.26698</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>-0.00363</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.237</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.0005200000000000001</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.35758</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.45617</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.3676</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.35631</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.52815</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.48556</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.76537</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.61538</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.5139</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.51503</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.14589</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.38299</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.5900700000000001</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.54364</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.27595</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.50231</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.50513</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.61739</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.5737300000000001</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.43438</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.42967</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40167</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.3336</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.33391</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.62524</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.43222</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.7575700000000001</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.35218</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.34336</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.54606</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.52776</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5077</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.51622</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.5116000000000001</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39518</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47739</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37464</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38206</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39334</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33863</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37244</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35786</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36107</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37738</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37731</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.36126</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38226</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42546</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.52867</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.65566</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.75312</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.44295</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.35574</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38978</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.31508</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.14179</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.29614</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.4491</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.08993999999999999</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.2947</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.30328</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>-0.0442</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.26438</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.2055</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.1147</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.2668</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.3022</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.25805</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.5921900000000001</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.22627</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.27438</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.29351</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.32252</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.32542</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.27384</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.5855900000000001</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.39317</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.33721</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>-0.01617</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.26514</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.29671</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.30731</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.26614</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.30138</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.32235</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.23232</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.16047</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.23477</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.26191</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.22966</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.27335</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.44052</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.42445</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.31605</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.27114</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.37536</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.47844</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.2919</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.70982</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.59211</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.2771</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.34212</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.8483099999999999</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.44019</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.38711</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.82974</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.29267</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.43838</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.59882</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.43915</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43385</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.40793</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.34458</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.30765</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.31042</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.36972</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.47409</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.36517</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38091</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40169</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.33464</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.3147799999999999</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.29531</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43287</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44899</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.30891</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37133</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.29479</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37005</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.3004</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.30506</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.2874</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.28998</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.30009</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.29189</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44852</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44288</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.3127799999999999</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.31623</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.31363</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.30964</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.21426</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.19314</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.18332</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.27176</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.02481</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>-0.02927</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.04344</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.01225</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.02856</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.12611</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.05207</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>-0.02829</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.18187</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.26987</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.27787</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.07226</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.21838</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.15072</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.20862</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.19573</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.24876</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29221</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.24114</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.28675</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.27977</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.29251</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.32405</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.28001</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.23209</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.29259</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.25179</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.22164</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.06295000000000001</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.28468</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.29548</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.2854100000000001</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.32358</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.36381</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.48164</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>-0.00138</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.50287</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.31844</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.30678</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.29267</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.32097</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.29152</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.37486</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.39576</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.38184</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.3032</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.31079</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.33047</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.31874</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.35307</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.34336</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34412</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.32086</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.30119</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.31961</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.31306</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.32918</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.32504</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.3008</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.26997</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.27355</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.47919</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.29091</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.30839</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.27355</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.29832</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.29956</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.28111</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.28302</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.27973</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.2806</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.28036</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.36448</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.32226</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39062</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.30004</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.30642</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.29856</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.29638</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.31182</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.27898</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.26141</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.26396</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.19444</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.10829</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.11245</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.08183</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.25008</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.21182</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.13268</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.28861</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.44963</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.28934</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.37619</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.21519</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>-0.04248</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>-0.04347</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.06115</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.27095</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.17565</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.04266</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>-0.007160000000000001</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.21276</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>-1e-05</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.03189</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.04921</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.07759000000000001</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.32581</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.20069</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.16561</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.20282</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.15081</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.19494</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.14178</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.19902</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.22674</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.27889</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.30866</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33699</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.25804</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.28772</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.30378</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.42001</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.46962</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.38054</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.36573</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.29629</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.30176</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.29861</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.29655</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.29266</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.25497</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.2911</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.2904</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29434</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.29227</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.29639</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.2922</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.29772</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.36771</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3012</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31107</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30026</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.29822</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.2753</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30414</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.29579</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.27361</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.27635</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29016</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29016</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29021</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29213</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29513</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.3013</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32421</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33293</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.2793</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26046</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.04075</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04514</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.04027</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.04002</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04267</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.0435</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04550999999999999</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.04652000000000001</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.04713000000000001</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04797</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04647</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04681</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04765</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04686999999999999</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04589</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04803</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04992</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.0465</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04801</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04921</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.0488</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.04649</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.04731</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.22001</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04642</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.04883</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05162</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.00211</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.1471</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.03759000000000001</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.09887</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.28979</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29181</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29269</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31371</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.32865</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.31717</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.36711</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.38544</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37761</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.40062</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.3954</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41228</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46764</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35341</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39653</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40014</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41729</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35519</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35132</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.66444</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40014</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44655</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42373</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42381</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33538</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32633</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35873</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35717</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34821</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33507</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32274</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30016</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.3228</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31617</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10243</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04263</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04589</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04507</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04484</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04484</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04484</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04399</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04179</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.03236</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04065999999999999</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10695</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.00109</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.0374</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.04688000000000001</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04106</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04123</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04115</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04372</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04366</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04354</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04104</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04045</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04326</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04031000000000001</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.03894</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04341</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.0437</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04105</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04213</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.03996</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04264</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.04992</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04303</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04642</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04599</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.20238</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14484</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29271</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29742</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30727</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30253</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29759</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29486</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29637</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29543</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29975</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29344</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.27143</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29636</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.30051</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.3102</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30697</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30327</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31728</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.32127</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35255</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34737</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36945</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36789</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33778</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33295</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.32299</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31338</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40741</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35258</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31133</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31712</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30396</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28361</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29789</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.2937</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.29058</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28382</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27355</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27371</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28342</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17439</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.16065</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17328</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14962</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16134</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.16072</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23965</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21615</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22875</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.27203</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28859</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29317</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29369</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28382</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28346</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28336</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.2709</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28323</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32548</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30786</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3172</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.3108</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.36094</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.27442</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>-0.02434</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.27425</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.3821</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.30136</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.08381999999999999</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.28996</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.29222</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.29219</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.39064</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.31399</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30115</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29887</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.3002</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15728</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.18845</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.28831</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.28825</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.27224</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32203</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.29635</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30059</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.30721</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50751</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79108</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6219199999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.39988</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49779</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78086</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92003</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.4943</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9282</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.90727</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.3197</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.39691</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.9304</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63888</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.22924</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.88967</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.58109</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.37407</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.06259</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5741499999999999</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.82782</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.81003</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.80691</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8813300000000001</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.89322</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.5277500000000001</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.43246</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.44432</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.48944</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.25142</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.8800800000000001</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.5517799999999999</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6659299999999999</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5492899999999999</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.51037</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.46122</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42946</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.44494</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45205</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39933</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45326</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42241</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35751</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40048</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36567</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.39692</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41534</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43439</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34435</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39162</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35108</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.37673</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.37391</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.36877</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.41385</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.36994</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45134</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40014</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40072</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58972</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42855</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5968600000000001</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60201</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.6445</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.45484</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.32147</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.35838</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.44742</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.8651599999999999</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.26266</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.65647</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.64061</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.77235</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.23337</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.4343</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.31508</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32638</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.3028</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>-0.03464</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.29581</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29418</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.27338</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.30319</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35945</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33258</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.31986</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.34006</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.34137</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30645</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.32339</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31274</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31411</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31288</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31527</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.3172</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32365</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32528</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32738</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35631</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34276</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33898</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.4103</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45282</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41535</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.3918</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37526</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35329</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="C125" t="n">
+        <v>1.02642</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36092</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.49992</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.5033299999999999</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.62249</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.6971000000000001</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.41546</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.4099100000000001</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.45094</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.51301</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.44931</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.36567</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38849</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40049</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50063</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35753</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38796</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34384</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35555</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37076</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35737</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36253</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31598</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31311</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33208</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33766</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30434</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29062</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30394</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28912</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.28079</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16474</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.28524</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30802</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30382</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.31406</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.2969</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26109</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20121</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27747</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29305</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.00344</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27597</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.29554</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.2755</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.2605</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.29526</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30518</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31299</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.2905</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.30392</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29102</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30904</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.2899</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34762</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25544</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32213</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.24865</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27493</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.33882</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31004</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.31763</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.42807</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.24472</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42323</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44699</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.31147</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42072</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40202</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40076</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59766</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8897699999999999</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.35774</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.13644</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.71194</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.80601</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.65125</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.59102</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45101</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45033</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50042</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43988</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43762</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41505</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42367</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5009</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43406</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41318</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43409</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39042</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42832</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45075</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39632</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42348</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43442</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41289</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40051</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42385</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39603</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40269</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.2723</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.2712</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.27319</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.28437</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.27582</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.29682</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.26124</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.2553</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.25288</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.25924</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.02132</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.23212</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.2741</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.25081</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24997</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.00621</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.14184</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.23865</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.36603</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.2878500000000001</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.04991</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.17516</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.28008</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.24631</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.08166</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.24916</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.26867</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.30104</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.25707</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.30328</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.28216</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.29793</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.29557</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.30831</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31457</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.3888</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40004</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34751</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.48818</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.43223</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36515</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.35446</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.60833</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46577</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.6836100000000001</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46676</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43964</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.3769</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42565</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.3882</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.37136</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33638</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34242</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32656</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.32006</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42577</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.3414</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34233</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33793</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32839</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32844</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32711</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32643</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31211</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32926</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32185</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32206</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32205</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31171</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32663</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31269</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.32166</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32234</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39375</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32763</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35173</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.40229</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37701</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35156</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.34041</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35671</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.31179</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31069</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.02046</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.29589</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.02787</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.29645</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.29415</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23725</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.14656</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.14926</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29531</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15622</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14482</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.1424</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14487</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.14381</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.25901</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.1455</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.26886</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.14339</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.05361999999999999</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.11482</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.11375</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.14766</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.14258</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.14783</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.2888</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.32468</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.30603</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.27892</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.30106</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.30936</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.30459</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.3082</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.38276</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34452</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38116</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34669</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36184</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38618</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45144</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40124</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39366</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40368</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.3996499999999999</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.4377200000000001</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.44183</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.44128</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44623</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44549</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.4043</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39189</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39907</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39278</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36197</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.35072</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3410899999999999</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.44359</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.39038</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.47037</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42545</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41747</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37056</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38263</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38209</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39467</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38138</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37028</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38076</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36053</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39164</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37072</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38081</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35066</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34767</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34061</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34522</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37067</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.30762</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.29486</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.008789999999999999</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>-0.01215</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.24823</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.24845</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.24076</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>-0.02513</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.18088</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.09032</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>-0.02744</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.14558</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>-0.02319</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>-0.02469</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.19769</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.17649</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.30314</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>-0.02035</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.19547</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.20593</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>-0.02747</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.18963</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.17825</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>-0.0226</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.2102</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>-0.02648</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.2073</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>-0.02695</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>-0.0009699999999999999</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.29855</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.28658</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.29132</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.32397</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.29729</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.31137</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.33217</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.33234</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.37008</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36858</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.37779</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.44743</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.46047</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.24955</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.42685</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38427</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35503</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35751</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.3551</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41771</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.5143</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34898</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36768</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.37076</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36055</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38083</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38039</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38578</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36064</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36663</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.42045</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37095</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39233</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38121</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35328</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34991</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35213</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34252</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34815</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34616</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34254</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34365</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34055</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34164</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34464</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36195</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31306</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.32952</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33958</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32598</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.31888</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33205</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32087</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.31153</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.30407</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.28478</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.26279</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.23734</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.28025</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.25137</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.27014</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.2779</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>-0.03286</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.25478</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24999</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.21073</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.07518999999999999</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.18471</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.24503</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.27136</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.25341</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.29841</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.31301</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.3058</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.27485</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.29748</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.32758</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.33748</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.42875</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.34917</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35841</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.31689</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.39363</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32387</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.33447</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.34389</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.33319</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.50673</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.41671</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.77878</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36886</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.45194</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.44917</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.33819</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.35088</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.46967</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.43799</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.41752</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.31113</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.35633</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.35887</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.32708</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.31248</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.31038</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.3485</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30496</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.3431</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33158</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32535</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32525</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32892</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32417</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.3269</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33136</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32128</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31974</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32309</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34668</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34121</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33587</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33917</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32168</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32149</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33455</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34879</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.35321</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.32947</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32326</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31677</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32352</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.3141</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.28422</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>-0.04037</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.28682</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.2869</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>-0.04188</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.31348</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28265</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.3138</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31865</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.28898</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.31603</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.32097</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.31701</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31958</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31338</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.30439</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.28776</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.34645</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.28929</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.32235</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36015</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34775</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.37795</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36751</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36997</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.3642</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37502</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36262</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39611</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38562</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37166</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40429</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38083</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.37186</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36087</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34357</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35276</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.36235</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.36098</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34666</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.35072</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.37006</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33702</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34509</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33624</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32815</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32513</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.31809</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31737</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31846</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.31901</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.31948</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.31719</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37082</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.30953</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32048</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31585</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32395</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.30414</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.31891</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.31927</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32971</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32464</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.32824</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.32341</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.3460299999999999</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.34833</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.7393</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.41649</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35515</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.34625</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36709</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.36065</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34828</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.3613</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36334</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35129</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.37861</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.38128</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38217</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38266</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42954</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40731</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.39065</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.39185</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6495299999999999</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.87788</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.48764</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.48792</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.46046</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39421</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34508</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32053</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41167</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37648</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37188</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36382</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.36018</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.36015</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.3632</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36124</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35419</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36117</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36121</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35739</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35259</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.36018</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.3464</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37112</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35881</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38005</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35652</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35851</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.31722</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.2615</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.13638</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.29139</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28417</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28272</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19534</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.24652</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.2785899999999999</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.02854</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27963</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.13092</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.0197</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28409</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.2378</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28744</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.24815</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30328</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>-0.00615</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.30535</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.14512</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29978</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>-0.02115</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.23477</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.23743</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.29726</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.29791</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.30702</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.30402</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.31045</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.29967</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.31425</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.33683</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34094</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.34091</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.29819</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.34239</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.4177</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.36825</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.40893</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.00156</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.88009</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.11221</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.46227</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.58738</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.47819</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.28193</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.45416</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.46012</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40228</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37686</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.48189</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43061</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41998</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37888</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37491</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36735</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.3602</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.49348</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.47523</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.45799</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.42158</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.4011</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40751</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41401</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.41142</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41982</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.40195</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.3983</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41406</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.41154</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39428</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38802</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41905</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38815</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41725</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39044</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40043</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40037</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41312</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40031</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45082</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45002</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.56137</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.50095</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45098</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.41687</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.4199</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.37552</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.32785</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.37078</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.37811</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.42726</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.3722</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.40592</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.29415</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32242</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.32512</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.31931</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.27681</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.27664</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.29439</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.17091</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>-0.005730000000000001</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.15395</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.04255</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.03504</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.29534</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>-0.03602</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.19294</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.17974</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.02685</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.10804</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.009810000000000001</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.26996</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.03734000000000001</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.32732</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.32736</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.31573</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.33298</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.32641</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.33952</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.33455</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.34135</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.35966</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.41565</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.48616</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.38919</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.50617</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.50845</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.42895</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.82512</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.17799</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.13743</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.35311</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.59672</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.98517</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.8744500000000001</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>1.63557</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>1.16024</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.31706</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.58309</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.9555800000000001</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.77336</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.75442</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.7583200000000001</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.56839</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.94498</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.5724900000000001</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.62133</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.6705099999999999</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.60777</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.5711499999999999</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.5548200000000001</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.54461</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.48883</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.64759</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.48403</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.50897</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.48374</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.44931</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.38134</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37617</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35691</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36588</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37719</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37135</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36028</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36588</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38704</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39035</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36675</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39983</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36761</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.42585</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.47342</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.3947</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38684</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34272</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32657</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.27979</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.29645</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.15876</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.34517</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.2741</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.34758</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.03885</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.31304</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35137</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.4084100000000001</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.37277</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.4528</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.40795</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46378</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.01493</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.1851</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30469</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29085</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31558</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35237</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34792</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34862</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.36519</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.36242</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.35616</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.38575</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.48757</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.35782</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.44258</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.42985</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.42621</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.40334</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.35468</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.37311</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.41733</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.46584</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.39506</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34258</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.41785</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.40122</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.42144</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.483</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38073</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.40615</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.45459</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.40871</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.3627</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33232</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44381</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.35703</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.36015</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.37819</v>
+      </c>
+      <c r="G135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.34861</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.34122</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="K135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.30213</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.30339</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.26249</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.30354</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.22295</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.27946</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.30232</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33484</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34066</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34566</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33067</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.34377</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.34386</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.32202</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.24931</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.33228</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32677</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.32104</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.23558</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.29836</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23731</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.24664</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.2521</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.04051</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.03685</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.1451</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29421</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.05781</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.17642</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04341</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25953</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.04092</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.14872</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.15241</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.05962</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30097</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.01085</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.11858</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.03838</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>-0.03971</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.14451</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28365</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>-0.03938000000000001</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>-0.02326</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.30108</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.02357</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.30838</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.32159</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.32577</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.32154</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.34584</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.34088</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34335</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30908</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.36925</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35467</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36221</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36434</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34485</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37435</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36734</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.37176</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.35157</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.35185</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.35142</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35138</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32429</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32578</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33178</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34131</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34091</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.34114</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33313</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32676</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.32153</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.32157</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31227</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31173</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31079</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31264</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31143</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.32155</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30981</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.3137200000000001</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30662</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29153</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.19194</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.18763</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.13076</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.14933</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.04839</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01619</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>-0.00147</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.04367</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.04145</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.13822</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.1905</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27694</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.22279</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.22341</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.22426</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.2285</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.23876</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.26569</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.24843</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.24168</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.23296</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.2979</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.24883</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.25247</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.23528</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.2537</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.24234</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.25977</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.24764</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.2608</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.32007</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.27526</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.27524</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.25793</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.21712</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.23768</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.21543</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.18475</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.08234</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>-0.04040999999999999</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.23508</v>
+      </c>
+      <c r="D137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E137" t="n">
+        <v>-0.04724</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.15369</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.15676</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.15715</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.02088</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.23294</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.21843</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.20036</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.16438</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.15891</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.13108</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.15837</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.1876</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.10807</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.12508</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.19034</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.15876</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.20983</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.18203</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.17026</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.22346</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.16922</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.22032</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.2901</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.22765</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.20953</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.2169</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.12982</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>-0.04333</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.33795</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.34233</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.44181</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.19321</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>-0.00118</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.17034</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.16674</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.008500000000000001</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>-0.04781000000000001</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>-0.02576</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.18653</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.26576</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.08018</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>-0.04912</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.01159</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.23519</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.253</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.28259</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.30628</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.30795</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.30424</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.32283</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.31273</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.31674</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.32592</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.34514</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.34701</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.20169</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.34555</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.35278</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.34425</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.34578</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.32253</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.33024</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.33076</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.33191</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32939</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.34082</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32629</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35538</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.36878</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.33614</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.33793</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.32981</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32731</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.10566</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32709</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33141</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.32208</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33277</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.32407</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.27631</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.33488</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.26121</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.31723</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.25516</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.12135</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.24485</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.32523</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.30659</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.31537</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.39752</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.29467</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.29371</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.2955</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.3012</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.29835</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.30159</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.3131</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.31057</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.29323</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>-0.007480000000000001</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.25693</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.26983</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30422</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.31212</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.18988</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.3126</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.1434</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.10632</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29012</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.30977</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31599</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32105</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32647</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32385</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34689</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34096</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.32814</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34029</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.3420299999999999</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.34636</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33314</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.34942</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.34825</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33837</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34778</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.35375</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37275</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.31079</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.33122</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35159</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.33499</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.33459</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.33846</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.34216</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36899</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35426</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31743</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33321</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32913</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33162</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33217</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.36519</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.24034</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31653</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32026</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.3295</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34524</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.26334</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33626</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.34072</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.3234</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.35124</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35066</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.27715</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.30743</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.2377</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>-0.03671</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.26057</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.25752</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.31868</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.31792</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.3463</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.29654</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.27451</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.28414</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.28254</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.26797</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.17703</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30797</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.38492</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.26526</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.26736</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.26339</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.29334</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.3464</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.32845</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.24854</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.28306</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.32425</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.30832</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.28239</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.01072</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.01587</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.28143</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.42422</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.33056</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.31019</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.28781</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.31108</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.52373</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.3343</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>-0.00907</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.31817</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.33003</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.3167</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.40571</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.5491900000000001</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.47889</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.38977</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.45634</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.43138</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>1.72594</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.50157</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.42898</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.5775</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40302</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38003</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.39057</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.37076</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.3858</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37274</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.37041</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36903</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.46782</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40018</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39052</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.34181</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37871</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.34207</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.35117</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35625</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35622</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.35074</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.36171</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.40016</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.36305</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36943</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.35086</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.29773</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.31057</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.32462</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.29125</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.46486</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.34398</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.30843</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.21047</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.17806</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.23535</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.27932</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.28938</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.30358</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.2775</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.29207</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.31393</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.26219</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33709</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.19381</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.2669</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.2775</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.31472</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.31263</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.31526</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.30734</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.29543</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.3138</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.31356</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.31603</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.36807</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.41514</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.39507</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.39216</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.46657</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.56062</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.5332</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.38231</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.46227</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.5520499999999999</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.46551</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.38065</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.49812</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.39848</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.53324</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.5209199999999999</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.34861</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.37211</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.5505599999999999</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.55323</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39877</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44498</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39143</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37592</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.38052</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.37114</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37689</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27245</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36994</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37398</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33596</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.35303</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.31083</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33179</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34492</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34084</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.33103</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33649</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33042</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.3038</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.3136</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.29753</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.29044</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.29541</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.29815</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.27097</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.26764</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.33913</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35691</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.2792</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.26652</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.26221</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.25461</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.24775</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.29031</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.23788</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.23659</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.25366</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.18978</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.2118</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.13558</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>-0.00321</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>-0.03811</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>-0.00301</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.01305</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.13164</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.01135</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.02279</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>-0.02303</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.23551</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>-0.01497</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.02179</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.03128</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.02211</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.01591</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.01841</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.02955</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.10444</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.06486</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.11908</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.13855</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.16622</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.22294</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.1812</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.18713</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.32832</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.29727</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.31486</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.20744</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.33306</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.24946</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.36667</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.38753</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.36817</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.36868</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.32057</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.39014</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.3863</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.37973</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.40524</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.39278</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.36419</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.36163</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37157</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.41925</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38894</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.38552</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.38496</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.39975</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.38083</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.01922</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.3405899999999999</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.36278</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.35358</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.31665</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.32772</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33371</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.3338</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.33148</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.38415</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.35862</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38001</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.37307</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.33495</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35857</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36041</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36329</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.3668</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35892</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.33371</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.30503</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.3078</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.29028</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.28359</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.27559</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.27092</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.23242</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.22622</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.19528</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.19972</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.21532</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>-0.01783</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>-0.01512</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>-0.01721</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>-0.01781</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.0361</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.07743999999999999</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>-0.03782</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.004730000000000001</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01404</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04423</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>-0.00881</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>-0.00929</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>-0.00291</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.15528</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>-0.01663</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>-0.01682</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>-0.01343</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.00032</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>-0.02087</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>-0.0198</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>-0.02629</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.05461999999999999</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.22649</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.18138</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.23265</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.29455</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.26919</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.43182</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.38424</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.3935</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36187</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.38166</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39947</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.35684</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38731</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.52824</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.41489</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38976</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.3843</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39786</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.38515</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.38671</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.40868</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.3614</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.38951</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.43154</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.39285</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.44561</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.38604</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.47429</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.45296</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.37552</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.48002</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.32359</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.5122000000000001</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.39185</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.39566</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.29907</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.36601</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35349</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36269</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.33642</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41716</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.33526</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37031</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.33302</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.34327</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.32795</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.30015</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.34516</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.31073</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.30677</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32357</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36461</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.33371</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.33232</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.23108</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.18555</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.17088</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.11203</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.14695</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.1732</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.16044</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.08637</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.10331</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.04765</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.06915</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.03667</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.03745</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.03815</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.03697</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04515</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.05108</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.05946</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03433</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.05628</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.0711</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.11338</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.13976</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.08566</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.16146</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.14304</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.08837</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.04599</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.21377</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.09448000000000001</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.09032999999999999</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.18596</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.12885</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.13984</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.16481</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.14505</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.17969</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.19854</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.19959</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.21235</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.25432</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.25821</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.25974</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.28166</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.36271</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.4044700000000001</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.33493</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.3189</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.27241</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.33633</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38812</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.3772799999999999</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37736</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.35518</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38531</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.41356</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.42053</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.49807</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.41031</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41844</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.44363</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.41535</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.3976</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.41581</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.41488</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38211</v>
       </c>
     </row>
   </sheetData>
